--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpOutputTask.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/dmpOutputTask.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>配置id</t>
   </si>
@@ -53,9 +53,6 @@
     <t>输入任务id</t>
   </si>
   <si>
-    <t xml:space="preserve"> 拓展字段</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 执行系统</t>
   </si>
   <si>
@@ -86,7 +83,7 @@
     <t>{.endTime}</t>
   </si>
   <si>
-    <t>{.typeId}</t>
+    <t>{.statusName}</t>
   </si>
   <si>
     <t>{.errorMessage}</t>
@@ -98,13 +95,10 @@
     <t>{.inputTaskId}</t>
   </si>
   <si>
-    <t>{.billTypeName}</t>
-  </si>
-  <si>
     <t>{.execSystem}</t>
   </si>
   <si>
-    <t>{.execUrl}</t>
+    <t>{.instanceId}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1309,13 +1303,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="15" width="30" customWidth="1"/>
+    <col min="1" max="14" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:17">
+    <row r="1" ht="15" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,58 +1352,52 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
